--- a/称量记录.xlsx
+++ b/称量记录.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143AC592-BDAB-4CF5-95F3-7FC1C6D270A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FCDD7A-5628-46D5-9D3A-91B5C3C933BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="16200" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>称样时间</t>
   </si>
@@ -31,40 +31,24 @@
     <t>试样描述</t>
   </si>
   <si>
-    <t>TN26070352001</t>
-  </si>
-  <si>
-    <t>TN26070355001</t>
-  </si>
-  <si>
-    <t>TN26070357001</t>
-  </si>
-  <si>
-    <t>TN26070359001</t>
-  </si>
-  <si>
-    <t>TN26070363001</t>
-  </si>
-  <si>
-    <t>TN26070366001</t>
-  </si>
-  <si>
-    <t>TN26070367001</t>
-  </si>
-  <si>
-    <t>填草颗粒</t>
-  </si>
-  <si>
-    <t>EPDM颗粒</t>
-  </si>
-  <si>
-    <t>人造草</t>
-  </si>
-  <si>
-    <t>人造草颗粒</t>
-  </si>
-  <si>
-    <t>减震垫</t>
+    <t>TN26070374001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>透明胶水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TN26070376001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色胶水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TN26070380001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -95,27 +79,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -125,7 +94,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -432,13 +401,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.46484375" customWidth="1"/>
     <col min="2" max="2" width="16.73046875" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="9.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -449,122 +418,43 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>0.5655</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>1.5654999999999999</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>2.5655000000000001</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>46224</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>3.5655000000000001</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>46224</v>
-      </c>
-      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C6">
-        <v>4.5655000000000001</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>46224</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>5.5655000000000001</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>46224</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>6.5655000000000001</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>46224</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>7.5655000000000001</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
